--- a/Design/Excel/GameHot/Datas/Game/UIEntity.xlsx
+++ b/Design/Excel/GameHot/Datas/Game/UIEntity.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr autoCompressPictures="1"/>
   <bookViews>
     <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" fullPrecision="0" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -29,73 +29,73 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>CSName</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>AssetName</t>
-  </si>
-  <si>
-    <t>EntityGroupName</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string&amp;group=ge</t>
-  </si>
-  <si>
-    <t>string#path=normal;UI/UIEntity/*.prefab</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>实体编号</t>
-  </si>
-  <si>
-    <t>实体编号代码名（程序填）</t>
-  </si>
-  <si>
-    <t>策划备注</t>
-  </si>
-  <si>
-    <t>资源名称</t>
-  </si>
-  <si>
-    <t>实体组名称</t>
-  </si>
-  <si>
-    <t>加载优先级</t>
-  </si>
-  <si>
-    <t>WidgetTest</t>
-  </si>
-  <si>
-    <t>UI</t>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntityGroupName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string&amp;group=ge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string#path=normal;UI/UIEntity/*.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实体编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实体编号代码名（程序填）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">策划备注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资源名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实体组名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加载优先级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WidgetTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -111,26 +111,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <charset/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -146,7 +146,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -177,7 +177,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -185,7 +185,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,7 +193,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -201,14 +201,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -216,42 +216,42 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -557,154 +557,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" xfId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -768,8 +768,8 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1060,7 +1060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
@@ -1145,26 +1145,17 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>